--- a/out-base.xlsx
+++ b/out-base.xlsx
@@ -28,6 +28,23 @@
 </workbook>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A37" authorId="0">
+      <text>
+        <r>
+          <t>Computed from Δ APIC + Δ Common Stock vs prior period (historical years) or equityIssuance assumption (projection years).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="499">
   <si>
@@ -286,7 +303,7 @@
     <t>Last Updated</t>
   </si>
   <si>
-    <t>April 27, 2026</t>
+    <t>April 28, 2026</t>
   </si>
   <si>
     <t>SECTION 3 — EGYPT REGULATORY / TAX</t>
@@ -28938,6 +28955,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/out-base.xlsx
+++ b/out-base.xlsx
@@ -22,6 +22,23 @@
 </workbook>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Driver assumptions populate projection columns only. Historical (A) columns show reference values back-derived from Historical Data when applicable; an empty historical cell does not mean the value is zero.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -588,6 +605,12 @@
     <t>Assumption</t>
   </si>
   <si>
+    <t>2024 (A)</t>
+  </si>
+  <si>
+    <t>2025 (A)</t>
+  </si>
+  <si>
     <t>VAT Enabled (1=Yes)</t>
   </si>
   <si>
@@ -616,12 +639,6 @@
   </si>
   <si>
     <t>Telecom Egypt — Income Statement</t>
-  </si>
-  <si>
-    <t>2024 (A)</t>
-  </si>
-  <si>
-    <t>2025 (A)</t>
   </si>
   <si>
     <t>Cost of Goods Sold</t>
@@ -1287,7 +1304,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);0"/>
+    <numFmt numFmtId="168" formatCode="#,##0;-#,##0;0"/>
     <numFmt numFmtId="169" formatCode="#,##0.00x"/>
     <numFmt numFmtId="170" formatCode="#,##0.0000x"/>
     <numFmt numFmtId="171" formatCode="#,##0.0000"/>
@@ -3310,10 +3327,10 @@
         <v>356</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -3331,7 +3348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>357</v>
       </c>
@@ -3435,14 +3452,14 @@
         <v>346908967872</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="89" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="86"/>
       <c r="C6" s="87"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="57" t="s">
         <v>361</v>
       </c>
@@ -3547,7 +3564,7 @@
         <v>154250764410.88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -3587,14 +3604,14 @@
         <v>192658203461.12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="86"/>
       <c r="C13" s="87"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="57" t="s">
         <v>365</v>
       </c>
@@ -3699,14 +3716,14 @@
         <v>13.331324080485558</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="89" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="86"/>
       <c r="C18" s="87"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="57" t="s">
         <v>368</v>
       </c>
@@ -3802,10 +3819,10 @@
         <v>371</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -3823,7 +3840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>372</v>
       </c>
@@ -3959,14 +3976,14 @@
         <v>51750000000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="86"/>
       <c r="C7" s="87"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="57" t="s">
         <v>377</v>
       </c>
@@ -4105,14 +4122,14 @@
         <v>73750000000</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="86"/>
       <c r="C13" s="87"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="57" t="s">
         <v>381</v>
       </c>
@@ -4251,14 +4268,14 @@
         <v>8853054857.243984</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="86"/>
       <c r="C19" s="87"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>386</v>
       </c>
@@ -12130,8 +12147,7 @@
   <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="8" width="16" customWidth="1"/>
+    <col min="1" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -12139,10 +12155,10 @@
         <v>181</v>
       </c>
       <c r="B1" s="56" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C1" s="56" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -12160,7 +12176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>111</v>
       </c>
@@ -12345,7 +12361,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D10" s="63">
         <f>IF(Assumptions!$B$67="Base Case",Scenarios!D41,IF(Assumptions!$B$67="Optimistic",Scenarios!D127,Scenarios!D213))</f>
@@ -12468,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="57" t="s">
         <v>124</v>
       </c>
@@ -12623,9 +12639,9 @@
         <v>0.023430178069353328</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="57" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -12703,7 +12719,7 @@
         <v>2900000000</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>135</v>
       </c>
@@ -12935,7 +12951,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="61" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D36" s="66">
         <v>0.05</v>
@@ -12955,7 +12971,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="58" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D37" s="64">
         <f>IF(Assumptions!$B$67="Base Case",Scenarios!D18,IF(Assumptions!$B$67="Optimistic",Scenarios!D104,Scenarios!D190))</f>
@@ -12980,7 +12996,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="61" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D38" s="66">
         <v>0.1</v>
@@ -13023,7 +13039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="57" t="s">
         <v>148</v>
       </c>
@@ -13325,7 +13341,7 @@
         <v>5039284000</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="57" t="s">
         <v>158</v>
       </c>
@@ -13695,7 +13711,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B62" s="59">
         <f>'Historical Data'!B47</f>
@@ -13723,7 +13739,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="58" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B63" s="59">
         <f>'Historical Data'!B51</f>
@@ -13783,7 +13799,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="67" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B66" s="67"/>
       <c r="C66" s="67"/>
@@ -13810,7 +13826,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="70" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B68" s="70"/>
       <c r="C68" s="70"/>
@@ -13828,6 +13844,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -13845,13 +13862,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -14034,14 +14051,14 @@
         <v>0.5800000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="86"/>
       <c r="C7" s="87"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="57" t="s">
         <v>195</v>
       </c>
@@ -14279,7 +14296,7 @@
         <v>49689575565.44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="89" t="s">
         <v>8</v>
       </c>
@@ -14385,7 +14402,7 @@
         <v>0.2928804935540295</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="89" t="s">
         <v>8</v>
       </c>
@@ -14590,7 +14607,7 @@
         <v>0.225</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -14925,7 +14942,7 @@
         <v>19290486823.912167</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="89" t="s">
         <v>8</v>
       </c>
@@ -14998,14 +15015,14 @@
         <v>17.092948903144027</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="86"/>
       <c r="C41" s="87"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="57" t="s">
         <v>219</v>
       </c>
@@ -15179,10 +15196,10 @@
         <v>225</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -15200,7 +15217,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>226</v>
       </c>
@@ -15436,7 +15453,7 @@
         <v>67323981023.804016</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="89" t="s">
         <v>8</v>
       </c>
@@ -15707,14 +15724,14 @@
         <v>302582184484.924</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="86"/>
       <c r="C19" s="87"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>238</v>
       </c>
@@ -15983,7 +16000,7 @@
         <v>71167658504.04384</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -16188,14 +16205,14 @@
         <v>138557658504.04382</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="89" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="86"/>
       <c r="C36" s="87"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="57" t="s">
         <v>248</v>
       </c>
@@ -16433,7 +16450,7 @@
         <v>164024525980.8802</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -16562,7 +16579,7 @@
         <v>256</v>
       </c>
       <c r="B1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C1" s="56" t="s">
         <v>11</v>
@@ -16580,7 +16597,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>257</v>
       </c>
@@ -16818,7 +16835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="57" t="s">
         <v>262</v>
       </c>
@@ -17114,13 +17131,13 @@
         <v>61732531214.7833</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="89" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="87"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>272</v>
       </c>
@@ -17300,13 +17317,13 @@
         <v>-43265586672</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="89" t="s">
         <v>8</v>
       </c>
       <c r="B30" s="87"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="57" t="s">
         <v>279</v>
       </c>
@@ -17544,7 +17561,7 @@
         <v>-11509450121.829948</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="89" t="s">
         <v>8</v>
       </c>
@@ -17637,7 +17654,7 @@
         <v>28036623400.11087</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="89" t="s">
         <v>8</v>
       </c>
@@ -17672,7 +17689,7 @@
         <v>18466944542.783302</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="89" t="s">
         <v>8</v>
       </c>
@@ -17722,8 +17739,8 @@
   <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="8" width="16" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -17731,10 +17748,10 @@
         <v>290</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -17752,7 +17769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>291</v>
       </c>
@@ -17990,7 +18007,7 @@
         <v>0.19373610648793288</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="57" t="s">
         <v>295</v>
       </c>
@@ -18129,7 +18146,7 @@
         <v>0.44962788070240667</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="57" t="s">
         <v>299</v>
       </c>
@@ -18367,7 +18384,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>304</v>
       </c>
@@ -18539,7 +18556,7 @@
         <v>4.29547334861017</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="57" t="s">
         <v>310</v>
       </c>
@@ -18678,7 +18695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="57" t="s">
         <v>315</v>
       </c>
@@ -18949,7 +18966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="57" t="s">
         <v>323</v>
       </c>
@@ -19154,7 +19171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="57" t="s">
         <v>330</v>
       </c>
@@ -19382,10 +19399,10 @@
         <v>337</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C1" s="72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>11</v>
@@ -19403,7 +19420,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>338</v>
       </c>
@@ -19542,14 +19559,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="86"/>
       <c r="C7" s="87"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="57" t="s">
         <v>343</v>
       </c>
@@ -19688,14 +19705,14 @@
         <v>3000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="86"/>
       <c r="C13" s="87"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="57" t="s">
         <v>348</v>
       </c>
@@ -19834,7 +19851,7 @@
         <v>6000000000</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
